--- a/docs/validation/V13_Cohort_Census.xlsx
+++ b/docs/validation/V13_Cohort_Census.xlsx
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F112" s="8" t="n"/>
     </row>
-    <row r="113" ht="28" customHeight="1">
+    <row r="113" ht="83.5" customHeight="1">
       <c r="B113" s="10" t="inlineStr">
         <is>
           <t>Items with no cohort year</t>
@@ -1761,13 +1761,13 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Items in DimItem with no movement, or sql/06 not re-run</t>
+          <t>sql/06 not re-run, or DimItem holds items that never moved</t>
         </is>
       </c>
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>Run V12; items that never moved have no cohort by design — record how many</t>
+          <t>Run V12. Items that never moved have no cohort year, so the check fails as written — the criterion counts every DimItem row. Either stop sql/04 loading items with no movement, or change the criterion in document 02 §9 first. Do not pass it by explanation.</t>
         </is>
       </c>
       <c r="F113" s="8" t="n"/>
